--- a/config/calendario_academico_26_27.xlsx
+++ b/config/calendario_academico_26_27.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jfrutos/Library/CloudStorage/Dropbox/PASAR A DISCO/COORDINACION GIM/Janux/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D185BEB-F544-544E-895B-02BA25871532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B89B5F-D5F3-0E4B-9BF3-FA364C3064BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="35840" windowHeight="20320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="17920" windowHeight="20320" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Periodos" sheetId="1" r:id="rId1"/>
@@ -22,56 +22,125 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="45">
+  <si>
+    <t>Festivos y Días No Lectivos</t>
+  </si>
+  <si>
+    <t>Cuatrimestre</t>
+  </si>
+  <si>
+    <t>Fecha (AAAA-MM-DD)</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Descripción (opcional)</t>
+  </si>
+  <si>
+    <t>1C</t>
+  </si>
+  <si>
+    <t>no_lectivo</t>
+  </si>
+  <si>
+    <t>Fiesta de Bienvenida</t>
+  </si>
+  <si>
+    <t>festivo</t>
+  </si>
+  <si>
+    <t>Cartagineses y Romanos</t>
+  </si>
+  <si>
+    <t>Apertura oficial del curso</t>
+  </si>
+  <si>
+    <t>Dia de la hispanidad</t>
+  </si>
+  <si>
+    <t>Puente de la constitución</t>
+  </si>
+  <si>
+    <t>Fiesta Inmaculada Concepción</t>
+  </si>
+  <si>
+    <t>2C</t>
+  </si>
+  <si>
+    <t>Festividad ETSII</t>
+  </si>
+  <si>
+    <t>Festividad de San José</t>
+  </si>
   <si>
     <t>Calendario Académico — Periodos</t>
   </si>
   <si>
-    <t>Cuatrimestre</t>
-  </si>
-  <si>
     <t>Campo</t>
   </si>
   <si>
-    <t>Fecha (AAAA-MM-DD)</t>
-  </si>
-  <si>
-    <t>1C</t>
-  </si>
-  <si>
     <t>Inicio 1er cuatrimestre</t>
   </si>
   <si>
     <t>Fin 1er cuatrimestre</t>
   </si>
   <si>
-    <t>2C</t>
-  </si>
-  <si>
     <t>Inicio 2º cuatrimestre</t>
   </si>
   <si>
     <t>Fin 2º cuatrimestre</t>
   </si>
   <si>
+    <t>── Periodos de Exámenes Finales ──</t>
+  </si>
+  <si>
+    <t>ENERO</t>
+  </si>
+  <si>
+    <t>Inicio conv. enero (1C)</t>
+  </si>
+  <si>
+    <t>2027-01-07</t>
+  </si>
+  <si>
+    <t>Fin conv. enero (1C)</t>
+  </si>
+  <si>
+    <t>JUNIO</t>
+  </si>
+  <si>
+    <t>Inicio conv. junio (2C)</t>
+  </si>
+  <si>
+    <t>2027-05-31</t>
+  </si>
+  <si>
+    <t>Fin conv. junio (2C)</t>
+  </si>
+  <si>
+    <t>2027-06-22</t>
+  </si>
+  <si>
+    <t>EXTRAORD</t>
+  </si>
+  <si>
+    <t>Inicio conv. extraordinaria</t>
+  </si>
+  <si>
+    <t>2027-06-24</t>
+  </si>
+  <si>
+    <t>Fin conv. extraordinaria</t>
+  </si>
+  <si>
+    <t>2027-07-17</t>
+  </si>
+  <si>
     <t>ℹ  Introduce las fechas en formato AAAA-MM-DD  (ej. 2026-09-08)</t>
   </si>
   <si>
-    <t>Festivos y Días No Lectivos</t>
-  </si>
-  <si>
-    <t>Tipo</t>
-  </si>
-  <si>
-    <t>Descripción (opcional)</t>
-  </si>
-  <si>
-    <t>festivo</t>
-  </si>
-  <si>
-    <t>no_lectivo</t>
-  </si>
-  <si>
     <t>Periodos de Vacaciones (solo 2º cuatrimestre)</t>
   </si>
   <si>
@@ -87,35 +156,14 @@
     <t>ℹ  Añade aquí los periodos de vacaciones de Semana Santa, Carnaval, etc.</t>
   </si>
   <si>
-    <t>Fiesta de Bienvenida</t>
-  </si>
-  <si>
-    <t>Cartagineses y Romanos</t>
-  </si>
-  <si>
-    <t>Apertura oficial del curso</t>
-  </si>
-  <si>
-    <t>Dia de la hispanidad</t>
-  </si>
-  <si>
-    <t>Fiesta Inmaculada Concepción</t>
-  </si>
-  <si>
-    <t>Puente de la constitución</t>
-  </si>
-  <si>
-    <t>Festividad ETSII</t>
-  </si>
-  <si>
-    <t>Festividad de San José</t>
+    <t>Festividad de Santo Tomás</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -161,8 +209,41 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF555555"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF6A7A8A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -217,8 +298,32 @@
         <bgColor rgb="FFFEE2E2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4B5563"/>
+        <bgColor rgb="FF4B5563"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCFCE7"/>
+        <bgColor rgb="FFDCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEE2E2"/>
+        <bgColor rgb="FFFEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF3C7"/>
+        <bgColor rgb="FFFEF3C7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -252,11 +357,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC8D4E0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC8D4E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC8D4E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC8D4E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -306,10 +426,49 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -615,7 +774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -624,29 +783,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
+      <c r="A1" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
     </row>
     <row r="2" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C3" s="7">
         <v>46272</v>
@@ -654,10 +813,10 @@
     </row>
     <row r="4" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C4" s="7">
         <v>46378</v>
@@ -665,10 +824,10 @@
     </row>
     <row r="5" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C5" s="8">
         <v>46419</v>
@@ -676,26 +835,100 @@
     </row>
     <row r="6" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C6" s="8">
         <v>46535</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
+    <row r="7" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
+    </row>
+    <row r="8" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="26">
+        <v>46417</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -703,7 +936,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -713,173 +946,199 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
+      <c r="A1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
     </row>
     <row r="2" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="14" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="15">
         <v>46283</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="14" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="15">
         <v>46290</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" s="15">
         <v>46296</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="14" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="15">
         <v>46307</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" s="11">
         <v>46363</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" s="13">
         <v>46364</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="16" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B9" s="15">
         <v>46458</v>
       </c>
       <c r="C9" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="10" t="s">
         <v>15</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="16" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B10" s="15">
         <v>46465</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="16" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B11" s="15">
         <v>46475</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D11" s="10"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="16" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B12" s="15">
         <v>46476</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D12" s="10"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="15">
+        <v>46415</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="15">
+        <v>46547</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="A3:A201" xr:uid="{00000000-0002-0000-0100-000000000000}">
-      <formula1>"1C,2C"</formula1>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="C3:C201" xr:uid="{00000000-0002-0000-0100-000000000000}">
+      <formula1>"festivo,no_lectivo"</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="C3:C201" xr:uid="{00000000-0002-0000-0100-000001000000}">
-      <formula1>"festivo,no_lectivo"</formula1>
+    <dataValidation type="list" sqref="A3:A300" xr:uid="{00000000-0002-0000-0100-000001000000}">
+      <formula1>"1C,2C,ENERO,JUNIO,EXTRAORD"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -896,40 +1155,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
+      <c r="A1" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
     </row>
     <row r="2" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9">
-        <v>46467</v>
+        <v>46468</v>
       </c>
       <c r="B3" s="9">
         <v>46474</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
+      <c r="A5" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="2">
